--- a/dist/denki-calc-kit.xlsx
+++ b/dist/denki-calc-kit.xlsx
@@ -881,11 +881,11 @@
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>IF(OR(B6="",D6="",E6="",F6=""),"",H6*E6*D6/(1000*F6))</f>
+        <f>IF(OR(B6="",D6="",E6="",F6="",N(F6)&lt;=0),"",H6*E6*D6/(1000*F6))</f>
         <v/>
       </c>
       <c r="J6" s="10">
-        <f>IF(OR(I6="",C6=""),"",I6/C6)</f>
+        <f>IF(OR(I6="",C6="",N(C6)&lt;=0),"",I6/C6)</f>
         <v/>
       </c>
       <c r="K6" s="11">
@@ -893,7 +893,7 @@
         <v/>
       </c>
       <c r="L6" s="9">
-        <f>IF(OR(H6="",D6="",E6="",C6="",G6=""),"",H6*E6*D6/(1000*C6*G6))</f>
+        <f>IF(OR(H6="",D6="",E6="",C6="",G6="",N(C6)&lt;=0,N(G6)&lt;=0),"",H6*E6*D6/(1000*C6*G6))</f>
         <v/>
       </c>
       <c r="M6" s="11">
@@ -914,11 +914,11 @@
         <v/>
       </c>
       <c r="I7" s="9">
-        <f>IF(OR(B7="",D7="",E7="",F7=""),"",H7*E7*D7/(1000*F7))</f>
+        <f>IF(OR(B7="",D7="",E7="",F7="",N(F7)&lt;=0),"",H7*E7*D7/(1000*F7))</f>
         <v/>
       </c>
       <c r="J7" s="10">
-        <f>IF(OR(I7="",C7=""),"",I7/C7)</f>
+        <f>IF(OR(I7="",C7="",N(C7)&lt;=0),"",I7/C7)</f>
         <v/>
       </c>
       <c r="K7" s="11">
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="L7" s="9">
-        <f>IF(OR(H7="",D7="",E7="",C7="",G7=""),"",H7*E7*D7/(1000*C7*G7))</f>
+        <f>IF(OR(H7="",D7="",E7="",C7="",G7="",N(C7)&lt;=0,N(G7)&lt;=0),"",H7*E7*D7/(1000*C7*G7))</f>
         <v/>
       </c>
       <c r="M7" s="11">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IF(OR(B8="",D8="",E8="",F8=""),"",H8*E8*D8/(1000*F8))</f>
+        <f>IF(OR(B8="",D8="",E8="",F8="",N(F8)&lt;=0),"",H8*E8*D8/(1000*F8))</f>
         <v/>
       </c>
       <c r="J8" s="10">
-        <f>IF(OR(I8="",C8=""),"",I8/C8)</f>
+        <f>IF(OR(I8="",C8="",N(C8)&lt;=0),"",I8/C8)</f>
         <v/>
       </c>
       <c r="K8" s="11">
@@ -959,7 +959,7 @@
         <v/>
       </c>
       <c r="L8" s="9">
-        <f>IF(OR(H8="",D8="",E8="",C8="",G8=""),"",H8*E8*D8/(1000*C8*G8))</f>
+        <f>IF(OR(H8="",D8="",E8="",C8="",G8="",N(C8)&lt;=0,N(G8)&lt;=0),"",H8*E8*D8/(1000*C8*G8))</f>
         <v/>
       </c>
       <c r="M8" s="11">
@@ -980,11 +980,11 @@
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>IF(OR(B9="",D9="",E9="",F9=""),"",H9*E9*D9/(1000*F9))</f>
+        <f>IF(OR(B9="",D9="",E9="",F9="",N(F9)&lt;=0),"",H9*E9*D9/(1000*F9))</f>
         <v/>
       </c>
       <c r="J9" s="10">
-        <f>IF(OR(I9="",C9=""),"",I9/C9)</f>
+        <f>IF(OR(I9="",C9="",N(C9)&lt;=0),"",I9/C9)</f>
         <v/>
       </c>
       <c r="K9" s="11">
@@ -992,7 +992,7 @@
         <v/>
       </c>
       <c r="L9" s="9">
-        <f>IF(OR(H9="",D9="",E9="",C9="",G9=""),"",H9*E9*D9/(1000*C9*G9))</f>
+        <f>IF(OR(H9="",D9="",E9="",C9="",G9="",N(C9)&lt;=0,N(G9)&lt;=0),"",H9*E9*D9/(1000*C9*G9))</f>
         <v/>
       </c>
       <c r="M9" s="11">
@@ -1013,11 +1013,11 @@
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IF(OR(B10="",D10="",E10="",F10=""),"",H10*E10*D10/(1000*F10))</f>
+        <f>IF(OR(B10="",D10="",E10="",F10="",N(F10)&lt;=0),"",H10*E10*D10/(1000*F10))</f>
         <v/>
       </c>
       <c r="J10" s="10">
-        <f>IF(OR(I10="",C10=""),"",I10/C10)</f>
+        <f>IF(OR(I10="",C10="",N(C10)&lt;=0),"",I10/C10)</f>
         <v/>
       </c>
       <c r="K10" s="11">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="L10" s="9">
-        <f>IF(OR(H10="",D10="",E10="",C10="",G10=""),"",H10*E10*D10/(1000*C10*G10))</f>
+        <f>IF(OR(H10="",D10="",E10="",C10="",G10="",N(C10)&lt;=0,N(G10)&lt;=0),"",H10*E10*D10/(1000*C10*G10))</f>
         <v/>
       </c>
       <c r="M10" s="11">
@@ -1046,11 +1046,11 @@
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>IF(OR(B11="",D11="",E11="",F11=""),"",H11*E11*D11/(1000*F11))</f>
+        <f>IF(OR(B11="",D11="",E11="",F11="",N(F11)&lt;=0),"",H11*E11*D11/(1000*F11))</f>
         <v/>
       </c>
       <c r="J11" s="10">
-        <f>IF(OR(I11="",C11=""),"",I11/C11)</f>
+        <f>IF(OR(I11="",C11="",N(C11)&lt;=0),"",I11/C11)</f>
         <v/>
       </c>
       <c r="K11" s="11">
@@ -1058,7 +1058,7 @@
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>IF(OR(H11="",D11="",E11="",C11="",G11=""),"",H11*E11*D11/(1000*C11*G11))</f>
+        <f>IF(OR(H11="",D11="",E11="",C11="",G11="",N(C11)&lt;=0,N(G11)&lt;=0),"",H11*E11*D11/(1000*C11*G11))</f>
         <v/>
       </c>
       <c r="M11" s="11">
@@ -1079,11 +1079,11 @@
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IF(OR(B12="",D12="",E12="",F12=""),"",H12*E12*D12/(1000*F12))</f>
+        <f>IF(OR(B12="",D12="",E12="",F12="",N(F12)&lt;=0),"",H12*E12*D12/(1000*F12))</f>
         <v/>
       </c>
       <c r="J12" s="10">
-        <f>IF(OR(I12="",C12=""),"",I12/C12)</f>
+        <f>IF(OR(I12="",C12="",N(C12)&lt;=0),"",I12/C12)</f>
         <v/>
       </c>
       <c r="K12" s="11">
@@ -1091,7 +1091,7 @@
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>IF(OR(H12="",D12="",E12="",C12="",G12=""),"",H12*E12*D12/(1000*C12*G12))</f>
+        <f>IF(OR(H12="",D12="",E12="",C12="",G12="",N(C12)&lt;=0,N(G12)&lt;=0),"",H12*E12*D12/(1000*C12*G12))</f>
         <v/>
       </c>
       <c r="M12" s="11">
@@ -1112,11 +1112,11 @@
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>IF(OR(B13="",D13="",E13="",F13=""),"",H13*E13*D13/(1000*F13))</f>
+        <f>IF(OR(B13="",D13="",E13="",F13="",N(F13)&lt;=0),"",H13*E13*D13/(1000*F13))</f>
         <v/>
       </c>
       <c r="J13" s="10">
-        <f>IF(OR(I13="",C13=""),"",I13/C13)</f>
+        <f>IF(OR(I13="",C13="",N(C13)&lt;=0),"",I13/C13)</f>
         <v/>
       </c>
       <c r="K13" s="11">
@@ -1124,7 +1124,7 @@
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>IF(OR(H13="",D13="",E13="",C13="",G13=""),"",H13*E13*D13/(1000*C13*G13))</f>
+        <f>IF(OR(H13="",D13="",E13="",C13="",G13="",N(C13)&lt;=0,N(G13)&lt;=0),"",H13*E13*D13/(1000*C13*G13))</f>
         <v/>
       </c>
       <c r="M13" s="11">
@@ -1145,11 +1145,11 @@
         <v/>
       </c>
       <c r="I14" s="9">
-        <f>IF(OR(B14="",D14="",E14="",F14=""),"",H14*E14*D14/(1000*F14))</f>
+        <f>IF(OR(B14="",D14="",E14="",F14="",N(F14)&lt;=0),"",H14*E14*D14/(1000*F14))</f>
         <v/>
       </c>
       <c r="J14" s="10">
-        <f>IF(OR(I14="",C14=""),"",I14/C14)</f>
+        <f>IF(OR(I14="",C14="",N(C14)&lt;=0),"",I14/C14)</f>
         <v/>
       </c>
       <c r="K14" s="11">
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>IF(OR(H14="",D14="",E14="",C14="",G14=""),"",H14*E14*D14/(1000*C14*G14))</f>
+        <f>IF(OR(H14="",D14="",E14="",C14="",G14="",N(C14)&lt;=0,N(G14)&lt;=0),"",H14*E14*D14/(1000*C14*G14))</f>
         <v/>
       </c>
       <c r="M14" s="11">
@@ -1178,11 +1178,11 @@
         <v/>
       </c>
       <c r="I15" s="9">
-        <f>IF(OR(B15="",D15="",E15="",F15=""),"",H15*E15*D15/(1000*F15))</f>
+        <f>IF(OR(B15="",D15="",E15="",F15="",N(F15)&lt;=0),"",H15*E15*D15/(1000*F15))</f>
         <v/>
       </c>
       <c r="J15" s="10">
-        <f>IF(OR(I15="",C15=""),"",I15/C15)</f>
+        <f>IF(OR(I15="",C15="",N(C15)&lt;=0),"",I15/C15)</f>
         <v/>
       </c>
       <c r="K15" s="11">
@@ -1190,7 +1190,7 @@
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>IF(OR(H15="",D15="",E15="",C15="",G15=""),"",H15*E15*D15/(1000*C15*G15))</f>
+        <f>IF(OR(H15="",D15="",E15="",C15="",G15="",N(C15)&lt;=0,N(G15)&lt;=0),"",H15*E15*D15/(1000*C15*G15))</f>
         <v/>
       </c>
       <c r="M15" s="11">
@@ -1211,11 +1211,11 @@
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>IF(OR(B16="",D16="",E16="",F16=""),"",H16*E16*D16/(1000*F16))</f>
+        <f>IF(OR(B16="",D16="",E16="",F16="",N(F16)&lt;=0),"",H16*E16*D16/(1000*F16))</f>
         <v/>
       </c>
       <c r="J16" s="10">
-        <f>IF(OR(I16="",C16=""),"",I16/C16)</f>
+        <f>IF(OR(I16="",C16="",N(C16)&lt;=0),"",I16/C16)</f>
         <v/>
       </c>
       <c r="K16" s="11">
@@ -1223,7 +1223,7 @@
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>IF(OR(H16="",D16="",E16="",C16="",G16=""),"",H16*E16*D16/(1000*C16*G16))</f>
+        <f>IF(OR(H16="",D16="",E16="",C16="",G16="",N(C16)&lt;=0,N(G16)&lt;=0),"",H16*E16*D16/(1000*C16*G16))</f>
         <v/>
       </c>
       <c r="M16" s="11">
@@ -1244,11 +1244,11 @@
         <v/>
       </c>
       <c r="I17" s="9">
-        <f>IF(OR(B17="",D17="",E17="",F17=""),"",H17*E17*D17/(1000*F17))</f>
+        <f>IF(OR(B17="",D17="",E17="",F17="",N(F17)&lt;=0),"",H17*E17*D17/(1000*F17))</f>
         <v/>
       </c>
       <c r="J17" s="10">
-        <f>IF(OR(I17="",C17=""),"",I17/C17)</f>
+        <f>IF(OR(I17="",C17="",N(C17)&lt;=0),"",I17/C17)</f>
         <v/>
       </c>
       <c r="K17" s="11">
@@ -1256,7 +1256,7 @@
         <v/>
       </c>
       <c r="L17" s="9">
-        <f>IF(OR(H17="",D17="",E17="",C17="",G17=""),"",H17*E17*D17/(1000*C17*G17))</f>
+        <f>IF(OR(H17="",D17="",E17="",C17="",G17="",N(C17)&lt;=0,N(G17)&lt;=0),"",H17*E17*D17/(1000*C17*G17))</f>
         <v/>
       </c>
       <c r="M17" s="11">
@@ -1277,11 +1277,11 @@
         <v/>
       </c>
       <c r="I18" s="9">
-        <f>IF(OR(B18="",D18="",E18="",F18=""),"",H18*E18*D18/(1000*F18))</f>
+        <f>IF(OR(B18="",D18="",E18="",F18="",N(F18)&lt;=0),"",H18*E18*D18/(1000*F18))</f>
         <v/>
       </c>
       <c r="J18" s="10">
-        <f>IF(OR(I18="",C18=""),"",I18/C18)</f>
+        <f>IF(OR(I18="",C18="",N(C18)&lt;=0),"",I18/C18)</f>
         <v/>
       </c>
       <c r="K18" s="11">
@@ -1289,7 +1289,7 @@
         <v/>
       </c>
       <c r="L18" s="9">
-        <f>IF(OR(H18="",D18="",E18="",C18="",G18=""),"",H18*E18*D18/(1000*C18*G18))</f>
+        <f>IF(OR(H18="",D18="",E18="",C18="",G18="",N(C18)&lt;=0,N(G18)&lt;=0),"",H18*E18*D18/(1000*C18*G18))</f>
         <v/>
       </c>
       <c r="M18" s="11">
@@ -1310,11 +1310,11 @@
         <v/>
       </c>
       <c r="I19" s="9">
-        <f>IF(OR(B19="",D19="",E19="",F19=""),"",H19*E19*D19/(1000*F19))</f>
+        <f>IF(OR(B19="",D19="",E19="",F19="",N(F19)&lt;=0),"",H19*E19*D19/(1000*F19))</f>
         <v/>
       </c>
       <c r="J19" s="10">
-        <f>IF(OR(I19="",C19=""),"",I19/C19)</f>
+        <f>IF(OR(I19="",C19="",N(C19)&lt;=0),"",I19/C19)</f>
         <v/>
       </c>
       <c r="K19" s="11">
@@ -1322,7 +1322,7 @@
         <v/>
       </c>
       <c r="L19" s="9">
-        <f>IF(OR(H19="",D19="",E19="",C19="",G19=""),"",H19*E19*D19/(1000*C19*G19))</f>
+        <f>IF(OR(H19="",D19="",E19="",C19="",G19="",N(C19)&lt;=0,N(G19)&lt;=0),"",H19*E19*D19/(1000*C19*G19))</f>
         <v/>
       </c>
       <c r="M19" s="11">
@@ -1343,11 +1343,11 @@
         <v/>
       </c>
       <c r="I20" s="9">
-        <f>IF(OR(B20="",D20="",E20="",F20=""),"",H20*E20*D20/(1000*F20))</f>
+        <f>IF(OR(B20="",D20="",E20="",F20="",N(F20)&lt;=0),"",H20*E20*D20/(1000*F20))</f>
         <v/>
       </c>
       <c r="J20" s="10">
-        <f>IF(OR(I20="",C20=""),"",I20/C20)</f>
+        <f>IF(OR(I20="",C20="",N(C20)&lt;=0),"",I20/C20)</f>
         <v/>
       </c>
       <c r="K20" s="11">
@@ -1355,7 +1355,7 @@
         <v/>
       </c>
       <c r="L20" s="9">
-        <f>IF(OR(H20="",D20="",E20="",C20="",G20=""),"",H20*E20*D20/(1000*C20*G20))</f>
+        <f>IF(OR(H20="",D20="",E20="",C20="",G20="",N(C20)&lt;=0,N(G20)&lt;=0),"",H20*E20*D20/(1000*C20*G20))</f>
         <v/>
       </c>
       <c r="M20" s="11">
@@ -1376,11 +1376,11 @@
         <v/>
       </c>
       <c r="I21" s="9">
-        <f>IF(OR(B21="",D21="",E21="",F21=""),"",H21*E21*D21/(1000*F21))</f>
+        <f>IF(OR(B21="",D21="",E21="",F21="",N(F21)&lt;=0),"",H21*E21*D21/(1000*F21))</f>
         <v/>
       </c>
       <c r="J21" s="10">
-        <f>IF(OR(I21="",C21=""),"",I21/C21)</f>
+        <f>IF(OR(I21="",C21="",N(C21)&lt;=0),"",I21/C21)</f>
         <v/>
       </c>
       <c r="K21" s="11">
@@ -1388,7 +1388,7 @@
         <v/>
       </c>
       <c r="L21" s="9">
-        <f>IF(OR(H21="",D21="",E21="",C21="",G21=""),"",H21*E21*D21/(1000*C21*G21))</f>
+        <f>IF(OR(H21="",D21="",E21="",C21="",G21="",N(C21)&lt;=0,N(G21)&lt;=0),"",H21*E21*D21/(1000*C21*G21))</f>
         <v/>
       </c>
       <c r="M21" s="11">
@@ -1409,11 +1409,11 @@
         <v/>
       </c>
       <c r="I22" s="9">
-        <f>IF(OR(B22="",D22="",E22="",F22=""),"",H22*E22*D22/(1000*F22))</f>
+        <f>IF(OR(B22="",D22="",E22="",F22="",N(F22)&lt;=0),"",H22*E22*D22/(1000*F22))</f>
         <v/>
       </c>
       <c r="J22" s="10">
-        <f>IF(OR(I22="",C22=""),"",I22/C22)</f>
+        <f>IF(OR(I22="",C22="",N(C22)&lt;=0),"",I22/C22)</f>
         <v/>
       </c>
       <c r="K22" s="11">
@@ -1421,7 +1421,7 @@
         <v/>
       </c>
       <c r="L22" s="9">
-        <f>IF(OR(H22="",D22="",E22="",C22="",G22=""),"",H22*E22*D22/(1000*C22*G22))</f>
+        <f>IF(OR(H22="",D22="",E22="",C22="",G22="",N(C22)&lt;=0,N(G22)&lt;=0),"",H22*E22*D22/(1000*C22*G22))</f>
         <v/>
       </c>
       <c r="M22" s="11">
@@ -1442,11 +1442,11 @@
         <v/>
       </c>
       <c r="I23" s="9">
-        <f>IF(OR(B23="",D23="",E23="",F23=""),"",H23*E23*D23/(1000*F23))</f>
+        <f>IF(OR(B23="",D23="",E23="",F23="",N(F23)&lt;=0),"",H23*E23*D23/(1000*F23))</f>
         <v/>
       </c>
       <c r="J23" s="10">
-        <f>IF(OR(I23="",C23=""),"",I23/C23)</f>
+        <f>IF(OR(I23="",C23="",N(C23)&lt;=0),"",I23/C23)</f>
         <v/>
       </c>
       <c r="K23" s="11">
@@ -1454,7 +1454,7 @@
         <v/>
       </c>
       <c r="L23" s="9">
-        <f>IF(OR(H23="",D23="",E23="",C23="",G23=""),"",H23*E23*D23/(1000*C23*G23))</f>
+        <f>IF(OR(H23="",D23="",E23="",C23="",G23="",N(C23)&lt;=0,N(G23)&lt;=0),"",H23*E23*D23/(1000*C23*G23))</f>
         <v/>
       </c>
       <c r="M23" s="11">
@@ -1475,11 +1475,11 @@
         <v/>
       </c>
       <c r="I24" s="9">
-        <f>IF(OR(B24="",D24="",E24="",F24=""),"",H24*E24*D24/(1000*F24))</f>
+        <f>IF(OR(B24="",D24="",E24="",F24="",N(F24)&lt;=0),"",H24*E24*D24/(1000*F24))</f>
         <v/>
       </c>
       <c r="J24" s="10">
-        <f>IF(OR(I24="",C24=""),"",I24/C24)</f>
+        <f>IF(OR(I24="",C24="",N(C24)&lt;=0),"",I24/C24)</f>
         <v/>
       </c>
       <c r="K24" s="11">
@@ -1487,7 +1487,7 @@
         <v/>
       </c>
       <c r="L24" s="9">
-        <f>IF(OR(H24="",D24="",E24="",C24="",G24=""),"",H24*E24*D24/(1000*C24*G24))</f>
+        <f>IF(OR(H24="",D24="",E24="",C24="",G24="",N(C24)&lt;=0,N(G24)&lt;=0),"",H24*E24*D24/(1000*C24*G24))</f>
         <v/>
       </c>
       <c r="M24" s="11">
@@ -1508,11 +1508,11 @@
         <v/>
       </c>
       <c r="I25" s="9">
-        <f>IF(OR(B25="",D25="",E25="",F25=""),"",H25*E25*D25/(1000*F25))</f>
+        <f>IF(OR(B25="",D25="",E25="",F25="",N(F25)&lt;=0),"",H25*E25*D25/(1000*F25))</f>
         <v/>
       </c>
       <c r="J25" s="10">
-        <f>IF(OR(I25="",C25=""),"",I25/C25)</f>
+        <f>IF(OR(I25="",C25="",N(C25)&lt;=0),"",I25/C25)</f>
         <v/>
       </c>
       <c r="K25" s="11">
@@ -1520,7 +1520,7 @@
         <v/>
       </c>
       <c r="L25" s="9">
-        <f>IF(OR(H25="",D25="",E25="",C25="",G25=""),"",H25*E25*D25/(1000*C25*G25))</f>
+        <f>IF(OR(H25="",D25="",E25="",C25="",G25="",N(C25)&lt;=0,N(G25)&lt;=0),"",H25*E25*D25/(1000*C25*G25))</f>
         <v/>
       </c>
       <c r="M25" s="11">
